--- a/mistral_translate_work/split_by_prompt/excel/rc_description/lang_multi_text/lang_multi_text__rc_description__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/rc_description/lang_multi_text/lang_multi_text__rc_description__part_0001.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Làm mới Cooldown chiêu Resonance Skill khi Rover bước vào trạng thái &lt;color=Highlight&gt;&lt;te href=850034&gt;Dark Surge&lt;/te&gt;&lt;/color&gt; bằng cách sử dụng Heavy Attack &lt;color=Highlight&gt;Devastation&lt;/color&gt;.</t>
+          <t>Làm mới Thời gian hồi chiêu Resonance Skill khi Rover bước vào trạng thái &lt;color=Highlight&gt;&lt;te href=850034&gt;Dark Surge&lt;/te&gt;&lt;/color&gt; bằng cách sử dụng Heavy Attack &lt;color=Highlight&gt;Devastation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Resonance Liberation &lt;color=Highlight&gt;Blazing Flames&lt;/color&gt; cấp {0} "&lt;te href=850041&gt;Thermobaric Bullets&lt;/te&gt;" và ngay lập tức đặt lại Cooldown chiêu của Resonance Skill &lt;color=Highlight&gt;Whizzing Fight Spirit&lt;/color&gt;.</t>
+          <t>Resonance Liberation &lt;color=Highlight&gt;Blazing Flames&lt;/color&gt; cấp {0} "&lt;te href=850041&gt;Thermobaric Bullets&lt;/te&gt;" và ngay lập tức đặt lại Thời gian hồi chiêu của Resonance Skill &lt;color=Highlight&gt;Whizzing Fight Spirit&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonance Skill &lt;color=Highlight&gt;Scroll Divination&lt;/color&gt; được kích hoạt, có {0} xác suất kỹ năng sẽ không bước vào Thời Gian Cooldown.</t>
+          <t>Mỗi khi Resonance Skill &lt;color=Highlight&gt;Scroll Divination&lt;/color&gt; được kích hoạt, có {0} xác suất kỹ năng sẽ không bước vào Thời Gian hồi.</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       <c r="M116" t="inlineStr">
         <is>
           <t>Khi tấn công trực tiếp và tiêu diệt mục tiêu bị &lt;color=Wind&gt;&lt;te href=850009&gt;Zeal&lt;/te&gt;&lt;/color&gt; của &lt;color=Highlight&gt;Cartethyia's&lt;/color&gt; hoặc &lt;color=Highlight&gt;Fleurdelys's&lt;/color&gt;, nhận &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; trong {0} giây.
-Trong trạng thái &lt;color=Highlight&gt;Zeal&lt;/color&gt;, khi tiêu diệt kẻ địch, đòn tấn công trực tiếp tiếp theo gây sát thương lên mục tiêu sẽ nâng &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; lên số tầng tối đa trong số kẻ địch bị tiêu diệt. Số tầng này không vượt quá giới hạn &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; tối đa hiện tại. &lt;color=Highlight&gt;Zeal&lt;/color&gt; sẽ bị loại bỏ sau đó và bước vào Cooldown {1} giây.
+Trong trạng thái &lt;color=Highlight&gt;Zeal&lt;/color&gt;, khi tiêu diệt kẻ địch, đòn tấn công trực tiếp tiếp theo gây sát thương lên mục tiêu sẽ nâng &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; lên số tầng tối đa trong số kẻ địch bị tiêu diệt. Số tầng này không vượt quá giới hạn &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; tối đa hiện tại. &lt;color=Highlight&gt;Zeal&lt;/color&gt; sẽ bị loại bỏ sau đó và bước vào Thời gian hồi {1} giây.
 Khi &lt;color=Highlight&gt;&lt;te href=850179&gt;Fleurdelys's&lt;/te&gt;&lt;/color&gt; của &lt;color=Highlight&gt;Conviction&lt;/color&gt; đạt 30/60/90/120, Crit. DMG của &lt;color=Highlight&gt;Fleurdelys's&lt;/color&gt; tăng {2} trong {3} giây, tối đa 4 tầng. Thời gian hiệu lực không được làm mới khi nhận tầng mới. Sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation - Blade of Howling Squall&lt;/color&gt;, hiệu ứng tăng Crit. DMG sẽ bị loại bỏ.</t>
         </is>
       </c>
@@ -8109,7 +8109,7 @@
         <is>
           <t>Kích hoạt &lt;color=Highlight&gt;Resonance Liberation - A Knight's Heartfelt Prayers&lt;/color&gt; sẽ tăng giới hạn tối đa của &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; trên mục tiêu trong phạm vi nhất định lên &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=đợt P=đợt SapTag=0}. Đòn tấn công tiếp theo gây sát thương trực tiếp lên mục tiêu sẽ áp đặt &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=đợt P=đợt SapTag=1} &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; lên tất cả mục tiêu trong phạm vi và kích hoạt ngay &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; một lần mà không tiêu hao các đợt &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt;.
 Hệ số sát thương của Kỹ Năng Basic, Kỹ Năng Nặng, Dodge Counter và Intro Skill của &lt;color=Highlight&gt;Cartethyia's&lt;/color&gt; tăng thêm {2}, còn hệ số sát thương của Kỹ Năng Trên Không tăng thêm {3}.
-Sau khi sử dụng &lt;color=Highlight&gt;Mid-air Attack - Cartethyia&lt;/color&gt;, mỗi loại Bóng Kiếm thu hồi sẽ giảm Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill - Cartethyia&lt;/color&gt; đi 1 giây.</t>
+Sau khi sử dụng &lt;color=Highlight&gt;Mid-air Attack - Cartethyia&lt;/color&gt;, mỗi loại Bóng Kiếm thu hồi sẽ giảm Thời gian hồi chiêu của &lt;color=Highlight&gt;Resonance Skill - Cartethyia&lt;/color&gt; đi 1 giây.</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Hệ số Sát Thương của &lt;color=Highlight&gt;Heavy Attack - Absolute Fullness&lt;/color&gt; được tăng thêm {0}. Khi sử dụng kỹ năng này, Iuno tái kích hoạt &lt;color=Highlight&gt;&lt;te href=141001&gt;Lunar Cycle&lt;/te&gt; - New Moon&lt;/color&gt;, nhận {1} điểm &lt;color=Highlight&gt;&lt;te href=141003&gt;Sentience&lt;/te&gt;&lt;/color&gt; và làm mới toàn bộ Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill - Arc Beyond the Edge&lt;/color&gt;.</t>
+          <t>Hệ số Sát Thương của &lt;color=Highlight&gt;Heavy Attack - Absolute Fullness&lt;/color&gt; được tăng thêm {0}. Khi sử dụng kỹ năng này, Iuno tái kích hoạt &lt;color=Highlight&gt;&lt;te href=141001&gt;Lunar Cycle&lt;/te&gt; - New Moon&lt;/color&gt;, nhận {1} điểm &lt;color=Highlight&gt;&lt;te href=141003&gt;Sentience&lt;/te&gt;&lt;/color&gt; và làm mới toàn bộ Thời gian hồi chiêu của &lt;color=Highlight&gt;Resonance Skill - Arc Beyond the Edge&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Cooldown chiêu của Resonance Skill &lt;color=Highlight&gt;Shift Trick&lt;/color&gt; giảm {0} giây.</t>
+          <t>Thời gian hồi chiêu của Resonance Skill &lt;color=Highlight&gt;Shift Trick&lt;/color&gt; giảm {0} giây.</t>
         </is>
       </c>
     </row>
@@ -16538,7 +16538,7 @@
       <c r="M243" t="inlineStr">
         <is>
           <t>Hệ số Sát Thương của &lt;color=Highlight&gt;Sweet Dream&lt;/color&gt; trong Forte Circuit được tăng thêm {0}.
-Forte Circuit &lt;color=Highlight&gt;Perennial&lt;/color&gt;: Trong vòng {1} giây sau khi sử dụng &lt;color=Highlight&gt;Ephemeral&lt;/color&gt;, nếu Concerto Energy đã đầy và &lt;color=Highlight&gt;Perennial&lt;/color&gt; không trong Cooldown chiêu, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Perennial&lt;/color&gt;.
+Forte Circuit &lt;color=Highlight&gt;Perennial&lt;/color&gt;: Trong vòng {1} giây sau khi sử dụng &lt;color=Highlight&gt;Ephemeral&lt;/color&gt;, nếu Concerto Energy đã đầy và &lt;color=Highlight&gt;Perennial&lt;/color&gt; không trong Thời gian hồi chiêu, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Perennial&lt;/color&gt;.
 Sử dụng &lt;color=Highlight&gt;Perennial&lt;/color&gt; sẽ tiêu hao {2} Concerto Energy và hồi phục {3} Cánh Hoa Crimson, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; tương đương {4} sát thương của &lt;color=Highlight&gt;Ephemeral&lt;/color&gt;, được tính là Sát Thương Basic Attack. Skill này có thể sử dụng mỗi {5} giây một lần.
 Sau khi sử dụng &lt;color=Highlight&gt;Budding Mode&lt;/color&gt;, Camellya bước vào &lt;color=Highlight&gt;&lt;te href=850021&gt;Perennial&lt;/te&gt;&lt;/color&gt; và loại bỏ toàn bộ Crimson Buds. Hệ số Sát Thương cộng thêm từ &lt;color=Highlight&gt;Sweet Dream&lt;/color&gt; trong Forte Circuit sẽ tăng lên {6}.
 Immune với gián đoạn khi sử dụng &lt;color=Highlight&gt;Perennial&lt;/color&gt;.</t>
@@ -19100,7 +19100,7 @@
       <c r="M282" t="inlineStr">
         <is>
           <t>Intro Skill &lt;color=Highlight&gt;Before Injection of Dawn&lt;/color&gt; và Kỹ Năng Kết Thúc &lt;color=Highlight&gt;Bow to the Last Light&lt;/color&gt; nhận thêm {0} Tăng Sát Thương.
-Resonance Skill &lt;color=Highlight&gt;Golden Reflux&lt;/color&gt; tăng Hệ Số Sát Thương thêm {1}, giảm Thời Gian Cooldown {2} giây và nhận thêm 1 lần tích lũy.</t>
+Resonance Skill &lt;color=Highlight&gt;Golden Reflux&lt;/color&gt; tăng Hệ Số Sát Thương thêm {1}, giảm Thời Gian hồi {2} giây và nhận thêm 1 lần tích lũy.</t>
         </is>
       </c>
     </row>
@@ -19726,7 +19726,7 @@
 &lt;size=10&gt;&lt;/size&gt;
 Khi Hiyuki rời trạng thái chiến đấu hoặc hồi phục sau khi bị hạ gục, sau {2} giây không chiến đấu, các hiệu ứng sau sẽ kích hoạt một lần:
 - Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, hồi phục &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=3} &lt;color=Highlight&gt;&lt;te href=110803&gt;Frostharden Iai&lt;/te&gt;&lt;/color&gt;.
-- Đặt lại Cooldown chiêu cho &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=4} &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt;.
+- Đặt lại Thời gian hồi chiêu cho &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=4} &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt;.
 - Restore thêm {6} điểm &lt;color=Highlight&gt;&lt;te href=110802&gt;Frostheart&lt;/te&gt;&lt;/color&gt; cho &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=5} sử dụng tiếp theo của &lt;color=Highlight&gt;Frostblight: Jade Cleave&lt;/color&gt; hoặc &lt;color=Highlight&gt;Frostblight: Petalfall&lt;/color&gt;.</t>
         </is>
       </c>
